--- a/data/trans_dic/IP04F-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente</t>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,49</t>
+          <t>3,61; 11,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,32</t>
+          <t>4,7; 12,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,59</t>
+          <t>4,55; 11,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,4</t>
+          <t>2,97; 9,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,8</t>
+          <t>4,8; 9,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,58</t>
+          <t>4,75; 9,46</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 13,37</t>
+          <t>7,12; 14,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,82</t>
+          <t>4,64; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,36</t>
+          <t>5,44; 11,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,49</t>
+          <t>5,52; 11,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,57</t>
+          <t>7,13; 11,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,68</t>
+          <t>5,65; 9,9</t>
         </is>
       </c>
     </row>
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,19</t>
+          <t>6,5; 14,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,29</t>
+          <t>4,1; 10,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 15,45</t>
+          <t>7,56; 15,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,3</t>
+          <t>5,42; 12,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 13,43</t>
+          <t>7,78; 13,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,31</t>
+          <t>5,56; 10,55</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 18,17</t>
+          <t>9,91; 18,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 17,68</t>
+          <t>9,39; 17,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,15</t>
+          <t>5,98; 13,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,68</t>
+          <t>5,39; 11,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 14,3</t>
+          <t>9,05; 14,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 13,06</t>
+          <t>8,15; 13,21</t>
         </is>
       </c>
     </row>
@@ -951,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,31</t>
+          <t>8,59; 12,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,93</t>
+          <t>7,26; 10,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,87</t>
+          <t>7,31; 10,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,55</t>
+          <t>6,22; 9,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,16</t>
+          <t>8,47; 11,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,73</t>
+          <t>7,24; 9,55</t>
         </is>
       </c>
     </row>
@@ -1001,4 +1002,706 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8938</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10554</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11646</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20583</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19098</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4938; 15101</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6224; 16771</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6975; 18263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4359; 13820</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13929; 28887</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13272; 26422</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>20408</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14062</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17926</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17973</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38335</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>32035</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14600; 28920</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9512; 20300</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12129; 26173</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12207; 25565</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>30504; 49203</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24047; 42158</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15396</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10663</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18267</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14517</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33663</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25181</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10092; 22007</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6357; 16107</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12518; 25577</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8925; 21143</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24966; 43162</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17784; 33727</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>28387</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27016</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19396</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16584</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47783</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>20483; 37457</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19479; 35351</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12415; 27337</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11087; 23875</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>37471; 59547</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>33687; 54577</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>73130</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>62296</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>140364</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>119913</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>60499; 87864</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>50824; 75219</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>54791; 79969</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45900; 69992</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>123057; 160411</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>104068; 137380</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04F-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Habitat-trans_dic.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,03</t>
+          <t>3,66; 11,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,66</t>
+          <t>4,94; 12,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,91</t>
+          <t>4,59; 12,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 9,42</t>
+          <t>3,33; 9,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,95</t>
+          <t>4,78; 9,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,46</t>
+          <t>4,77; 9,43</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 14,1</t>
+          <t>7,29; 13,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,9</t>
+          <t>4,35; 9,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 11,73</t>
+          <t>5,29; 11,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,57</t>
+          <t>5,44; 11,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,49</t>
+          <t>6,91; 11,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,9</t>
+          <t>5,81; 9,95</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 14,16</t>
+          <t>6,63; 14,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,39</t>
+          <t>4,07; 10,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 15,45</t>
+          <t>7,34; 15,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,84</t>
+          <t>5,59; 13,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 13,45</t>
+          <t>7,95; 13,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,55</t>
+          <t>5,83; 10,61</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,91; 18,12</t>
+          <t>9,97; 18,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 17,04</t>
+          <t>9,49; 17,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,17</t>
+          <t>6,12; 13,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 11,6</t>
+          <t>5,09; 11,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,37</t>
+          <t>8,99; 14,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 13,21</t>
+          <t>8,31; 13,36</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,48</t>
+          <t>8,75; 12,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 10,75</t>
+          <t>7,2; 10,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,67</t>
+          <t>7,37; 10,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,48</t>
+          <t>6,36; 9,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,04</t>
+          <t>8,49; 11,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,55</t>
+          <t>7,27; 9,75</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4938; 15101</t>
+          <t>5010; 15291</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6224; 16771</t>
+          <t>6549; 16372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6975; 18263</t>
+          <t>7036; 18429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4359; 13820</t>
+          <t>4877; 14564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13929; 28887</t>
+          <t>13878; 28819</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13272; 26422</t>
+          <t>13305; 26316</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14600; 28920</t>
+          <t>14953; 27492</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9512; 20300</t>
+          <t>8910; 20229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12129; 26173</t>
+          <t>11789; 25766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12207; 25565</t>
+          <t>12026; 25909</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30504; 49203</t>
+          <t>29588; 48366</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24047; 42158</t>
+          <t>24759; 42371</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10092; 22007</t>
+          <t>10299; 22529</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6357; 16107</t>
+          <t>6311; 16693</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12518; 25577</t>
+          <t>12145; 26023</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8925; 21143</t>
+          <t>9204; 22049</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24966; 43162</t>
+          <t>25513; 43907</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17784; 33727</t>
+          <t>18651; 33906</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20483; 37457</t>
+          <t>20611; 38669</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19479; 35351</t>
+          <t>19675; 36529</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12415; 27337</t>
+          <t>12704; 27094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11087; 23875</t>
+          <t>10475; 23412</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37471; 59547</t>
+          <t>37238; 59826</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33687; 54577</t>
+          <t>34327; 55203</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60499; 87864</t>
+          <t>61583; 87539</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50824; 75219</t>
+          <t>50423; 73028</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54791; 79969</t>
+          <t>55270; 80863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45900; 69992</t>
+          <t>46929; 69529</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>123057; 160411</t>
+          <t>123474; 160610</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>104068; 137380</t>
+          <t>104562; 140196</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04F-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Habitat-trans_dic.xlsx
@@ -520,13 +520,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -594,22 +594,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 11,17</t>
+          <t>4,57; 11,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 12,35</t>
+          <t>3,01; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 12,01</t>
+          <t>3,39; 10,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,93</t>
+          <t>4,53; 12,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,93</t>
+          <t>5,03; 9,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,43</t>
+          <t>4,61; 9,58</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>9,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>6,86%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,41</t>
+          <t>5,38; 11,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 9,87</t>
+          <t>5,53; 11,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 11,55</t>
+          <t>7,12; 13,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 11,72</t>
+          <t>4,33; 9,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 11,3</t>
+          <t>7,04; 11,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,95</t>
+          <t>5,63; 9,68</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>9,91%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>6,88%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 14,5</t>
+          <t>7,35; 15,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,77</t>
+          <t>5,8; 13,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,72</t>
+          <t>6,65; 14,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,39</t>
+          <t>4,23; 10,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,68</t>
+          <t>7,84; 13,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,61</t>
+          <t>5,49; 10,31</t>
         </is>
       </c>
     </row>
@@ -834,22 +834,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>13,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>13,02%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 18,71</t>
+          <t>6,14; 13,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 17,61</t>
+          <t>5,32; 11,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,05</t>
+          <t>9,79; 18,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,38</t>
+          <t>9,31; 17,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 14,44</t>
+          <t>8,85; 14,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 13,36</t>
+          <t>8,16; 13,06</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,43</t>
+          <t>7,4; 10,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,43</t>
+          <t>6,4; 9,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,79</t>
+          <t>8,67; 12,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,42</t>
+          <t>7,45; 10,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,05</t>
+          <t>8,43; 11,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,75</t>
+          <t>7,19; 9,73</t>
         </is>
       </c>
     </row>
@@ -1032,13 +1032,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -1106,22 +1106,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11646</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>8938</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>10554</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11646</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8544</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5010; 15291</t>
+          <t>7007; 17776</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6549; 16372</t>
+          <t>4420; 13784</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7036; 18429</t>
+          <t>4638; 14371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4877; 14564</t>
+          <t>6001; 16328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13878; 28819</t>
+          <t>14590; 28450</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13305; 26316</t>
+          <t>12874; 26752</t>
         </is>
       </c>
     </row>
@@ -1224,22 +1224,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17926</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17973</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>20408</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>14062</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17926</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14953; 27492</t>
+          <t>12005; 25348</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8910; 20229</t>
+          <t>12217; 25389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11789; 25766</t>
+          <t>14604; 27418</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12026; 25909</t>
+          <t>8871; 20118</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29588; 48366</t>
+          <t>30150; 49541</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24759; 42371</t>
+          <t>23975; 41217</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1380,22 +1380,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18267</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14517</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>15396</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>10663</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18267</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14517</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10299; 22529</t>
+          <t>12162; 25574</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6311; 16693</t>
+          <t>9551; 21907</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12145; 26023</t>
+          <t>10338; 22053</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9204; 22049</t>
+          <t>6559; 15948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25513; 43907</t>
+          <t>25144; 43111</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18651; 33906</t>
+          <t>17558; 32964</t>
         </is>
       </c>
     </row>
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1498,22 +1498,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19396</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16584</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>28387</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>27016</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19396</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20611; 38669</t>
+          <t>12746; 27298</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19675; 36529</t>
+          <t>10944; 24039</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12704; 27094</t>
+          <t>20234; 37557</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10475; 23412</t>
+          <t>19320; 36665</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37238; 59826</t>
+          <t>36662; 59232</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34327; 55203</t>
+          <t>33696; 53943</t>
         </is>
       </c>
     </row>
@@ -1578,22 +1578,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1616,22 +1616,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>62296</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61583; 87539</t>
+          <t>55435; 81500</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50423; 73028</t>
+          <t>47226; 70514</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55270; 80863</t>
+          <t>61013; 86633</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46929; 69529</t>
+          <t>52170; 76515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>123474; 160610</t>
+          <t>122576; 162201</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>104562; 140196</t>
+          <t>103401; 139952</t>
         </is>
       </c>
     </row>
